--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -9424,9 +9424,6 @@
       <c r="K995" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C1:E1"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1"/>
     <hyperlink ref="A6" r:id="rId2"/>
